--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486272_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486272_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8821</v>
+        <v>5.0951</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7117</v>
+        <v>3.1096</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1705</v>
+        <v>1.9855</v>
       </c>
       <c r="G2" t="n">
         <v>4.1778</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4868</v>
+        <v>1.6998</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9972</v>
+        <v>1.3952</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4896</v>
+        <v>0.3046</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1542</v>
+        <v>2.6456</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8907</v>
+        <v>1.4437</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2635</v>
+        <v>1.2019</v>
       </c>
       <c r="G3" t="n">
         <v>2.4863</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8854</v>
+        <v>0.3767</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4711</v>
+        <v>0.024</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4143</v>
+        <v>0.3527</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3293</v>
+        <v>1.8284</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4896</v>
+        <v>1.2661</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8397</v>
+        <v>0.5623</v>
       </c>
       <c r="G4" t="n">
         <v>0.7792</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4626</v>
+        <v>0.9617</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2522</v>
+        <v>1.0287</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2104</v>
+        <v>-0.067</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5649999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0606</v>
+        <v>1.6636</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0695</v>
+        <v>0.7342</v>
       </c>
       <c r="F5" t="n">
-        <v>0.991</v>
+        <v>0.9294</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6264999999999999</v>
@@ -844,13 +844,13 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>1.86</v>
+        <v>1.4631</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4577</v>
+        <v>1.1224</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4023</v>
+        <v>0.3407</v>
       </c>
       <c r="V5" t="n">
         <v>0.1745</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1606</v>
+        <v>1.5657</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9199000000000001</v>
+        <v>1.6822</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2407</v>
+        <v>-0.1165</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1632</v>
+        <v>2.3242</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1887</v>
+        <v>-0.3772</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9745</v>
+        <v>2.7014</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2021</v>
+        <v>2.0199</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2674</v>
+        <v>-0.5078</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.9347</v>
+        <v>2.5277</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0389</v>
+        <v>0.3043</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.1306</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0399</v>
+        <v>0.1737</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>1.389</v>
+        <v>1.0665</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8843</v>
+        <v>0.9674</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4952</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9347</v>
+        <v>-2.2599</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3904</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1405</v>
+        <v>1.5365</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3886</v>
+        <v>0.5689</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7519</v>
+        <v>0.9677</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1986</v>
@@ -1000,13 +1000,13 @@
         <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7519</v>
+        <v>1.1479</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1837</v>
+        <v>1.3639</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4318</v>
+        <v>-0.216</v>
       </c>
       <c r="V7" t="n">
         <v>0.9347</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1003</v>
+        <v>1.3432</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2784</v>
+        <v>-0.2683</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1781</v>
+        <v>1.6115</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3242</v>
+        <v>0.8166</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3772</v>
+        <v>0.003</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7014</v>
+        <v>0.8136</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0199</v>
+        <v>0.1895</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5078</v>
+        <v>0.0365</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5277</v>
+        <v>0.153</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3043</v>
+        <v>0.6271</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1306</v>
+        <v>-0.0335</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1737</v>
+        <v>0.6606</v>
       </c>
       <c r="P8" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6011</v>
+        <v>0.1139</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5636</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0375</v>
+        <v>0.0273</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.2599</v>
+        <v>0.1952</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2599</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9656</v>
+        <v>0.571</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4918</v>
+        <v>0.3611</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4573</v>
+        <v>0.2099</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8166</v>
+        <v>-1.1632</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003</v>
+        <v>-0.1887</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8136</v>
+        <v>-0.9745</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1895</v>
+        <v>-1.2021</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0365</v>
+        <v>-0.2674</v>
       </c>
       <c r="L9" t="n">
-        <v>0.153</v>
+        <v>-0.9347</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6271</v>
+        <v>0.0389</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0335</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6606</v>
+        <v>-0.0399</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2638</v>
+        <v>0.7994</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.137</v>
+        <v>1.3255</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1268</v>
+        <v>-0.5261</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1952</v>
+        <v>0.9347</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.5443</v>
+        <v>1.3252</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7395</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.0336</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1394</v>
+        <v>0.4315</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.65</v>
+        <v>-0.4651</v>
       </c>
       <c r="G10" t="n">
         <v>1.5014</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2278</v>
+        <v>0.7048</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6441</v>
+        <v>0.9361</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4163</v>
+        <v>-0.2313</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9347</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7643</v>
+        <v>-0.3605</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0295</v>
+        <v>0.3742</v>
       </c>
       <c r="F11" t="n">
         <v>-0.7347</v>
@@ -1312,10 +1312,10 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2175</v>
+        <v>0.1863</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3701</v>
+        <v>0.7739</v>
       </c>
       <c r="U11" t="n">
         <v>-0.5876</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3852</v>
+        <v>-0.6774</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5879</v>
+        <v>-1.4677</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7974</v>
+        <v>0.7903</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9948</v>
+        <v>-1.8506</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.433</v>
+        <v>-1.9008</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5618</v>
+        <v>0.0502</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2935</v>
+        <v>-2.0433</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.1987</v>
+        <v>-1.8154</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0948</v>
+        <v>-0.2279</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7013</v>
+        <v>0.1927</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2344</v>
+        <v>-0.0854</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.467</v>
+        <v>0.2781</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4796</v>
+        <v>0.3031</v>
       </c>
       <c r="T12" t="n">
         <v>0.5756</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.096</v>
+        <v>-0.2725</v>
       </c>
       <c r="V12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.5407</v>
+        <v>-1.2427</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3618</v>
+        <v>-0.4761</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8211000000000001</v>
+        <v>-0.7665</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8506</v>
+        <v>-2.9948</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9008</v>
+        <v>-2.433</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0502</v>
+        <v>-0.5618</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.0433</v>
+        <v>-2.2935</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.8154</v>
+        <v>-2.1987</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2279</v>
+        <v>-0.0948</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1927</v>
+        <v>-0.7013</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0854</v>
+        <v>-0.2344</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2781</v>
+        <v>-0.467</v>
       </c>
       <c r="P13" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5601</v>
+        <v>0.6222</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3184</v>
+        <v>0.6874</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2417</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.5924</v>
+        <v>13.9349</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4168</v>
+        <v>7.7594</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1755</v>
+        <v>6.175700000000001</v>
       </c>
       <c r="G14" t="n">
         <v>5.662100000000001</v>
@@ -1519,7 +1519,7 @@
         <v>7.227600000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6792</v>
+        <v>4.679200000000002</v>
       </c>
       <c r="K14" t="n">
         <v>-3.692</v>
@@ -1528,7 +1528,7 @@
         <v>8.371199999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9828999999999998</v>
+        <v>0.9828999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>2.1265</v>
@@ -1546,10 +1546,10 @@
         <v>13.0504</v>
       </c>
       <c r="S14" t="n">
-        <v>9.102800000000002</v>
+        <v>9.445399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>9.9442</v>
+        <v>10.2866</v>
       </c>
       <c r="U14" t="n">
         <v>-0.8413</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3109</v>
+        <v>3.7188</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9266</v>
+        <v>3.3737</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6157</v>
+        <v>0.3451</v>
       </c>
       <c r="G15" t="n">
         <v>4.0682</v>
@@ -1624,13 +1624,13 @@
         <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1923</v>
+        <v>-0.7844</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4675</v>
+        <v>-0.0204</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.7248</v>
+        <v>-0.764</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8298</v>
+        <v>2.5877</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1997</v>
+        <v>1.8703</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6301</v>
+        <v>0.7174</v>
       </c>
       <c r="G16" t="n">
         <v>2.479</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4317</v>
+        <v>0.3263</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3305</v>
+        <v>0.3401</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1012</v>
+        <v>-0.0138</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4569</v>
+        <v>2.4729</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1762</v>
+        <v>3.2879</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7193</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>4.4639</v>
@@ -1780,13 +1780,13 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.877</v>
+        <v>-0.861</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0649</v>
+        <v>0.0469</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.8122</v>
+        <v>-0.9079</v>
       </c>
       <c r="V17" t="n">
         <v>-1.13</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7363</v>
+        <v>0.3265</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1193</v>
+        <v>0.1135</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.383</v>
+        <v>0.213</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0018</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.173</v>
+        <v>-0.2367</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5057</v>
+        <v>0.4999</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3327</v>
+        <v>-0.7367</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>M. FRIERSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9056</v>
+        <v>-0.8595</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1056</v>
+        <v>-1.3422</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2</v>
+        <v>0.4826</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2005</v>
+        <v>-1.4217</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6331</v>
+        <v>0.5959</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5674</v>
+        <v>-2.0176</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2943</v>
+        <v>-1.2965</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4473</v>
+        <v>0.3832</v>
       </c>
       <c r="L19" t="n">
-        <v>0.153</v>
+        <v>-1.6797</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9062</v>
+        <v>-0.1252</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1858</v>
+        <v>0.2127</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7204</v>
+        <v>-0.3379</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8376</v>
+        <v>-0.3524</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4937</v>
+        <v>-0.0457</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6561</v>
+        <v>-0.3067</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1952</v>
+        <v>-0.3904</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FRIERSON</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5006</v>
+        <v>-1.7006</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9009</v>
+        <v>-1.5764</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4004</v>
+        <v>-0.1243</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4217</v>
+        <v>-0.2111</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5959</v>
+        <v>0.4591</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0176</v>
+        <v>-0.6702</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2965</v>
+        <v>0.4131</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3832</v>
+        <v>1.0434</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.6797</v>
+        <v>-0.6303</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1252</v>
+        <v>-0.6241</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2127</v>
+        <v>-0.5843</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3379</v>
+        <v>-0.0399</v>
       </c>
       <c r="P20" t="n">
-        <v>1.305</v>
+        <v>-1.305</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.3797</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6044</v>
+        <v>0.2079</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.389</v>
+        <v>-0.5876</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3904</v>
+        <v>0.1952</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.04</v>
+        <v>-1.7251</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2085</v>
+        <v>-2.2232</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8316</v>
+        <v>0.498</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5804</v>
+        <v>-2.2005</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3048</v>
+        <v>-1.6331</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7244</v>
+        <v>-0.5674</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6398</v>
+        <v>-1.2943</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7205</v>
+        <v>-1.4473</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3603</v>
+        <v>0.153</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2202</v>
+        <v>-0.9062</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5843</v>
+        <v>-0.1858</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6359</v>
+        <v>-0.7204</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.2626</v>
+        <v>0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5676</v>
+        <v>-1.305</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0872</v>
+        <v>0.018</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8292</v>
+        <v>0.3761</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9164</v>
+        <v>-0.3581</v>
       </c>
       <c r="V21" t="n">
-        <v>1.8902</v>
+        <v>-0.1952</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1104</v>
+        <v>-2.1775</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6881</v>
+        <v>-1.7673</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4223</v>
+        <v>-0.4103</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2111</v>
+        <v>-0.5804</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4591</v>
+        <v>-1.3048</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6702</v>
+        <v>0.7244</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4131</v>
+        <v>0.6398</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0434</v>
+        <v>-0.7205</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6303</v>
+        <v>1.3603</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6241</v>
+        <v>-1.2202</v>
       </c>
       <c r="N22" t="n">
         <v>-0.5843</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0399</v>
+        <v>-0.6359</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.305</v>
+        <v>-3.2626</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3926</v>
+        <v>-4.5676</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7895</v>
+        <v>-0.2247</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0961</v>
+        <v>0.2704</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8857</v>
+        <v>-0.4951</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1952</v>
+        <v>1.8902</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>1.8902</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9947</v>
+        <v>-3.3794</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0213</v>
+        <v>-1.9096</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9734</v>
+        <v>-1.4698</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1657</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2417</v>
+        <v>-0.6264</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1214</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1204</v>
+        <v>-0.6168</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3698</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. HOLLOWELL</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6829</v>
+        <v>-3.6605</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8113</v>
+        <v>-3.3028</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8716</v>
+        <v>-0.3577</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.7596</v>
+        <v>-4.3323</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8583</v>
+        <v>-0.0579</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.9013</v>
+        <v>-4.2743</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1808</v>
+        <v>-4.1696</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5959</v>
+        <v>-1.3806</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5849</v>
+        <v>-2.789</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5788</v>
+        <v>-0.1627</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2624</v>
+        <v>1.3227</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3164</v>
+        <v>-1.4854</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8358</v>
+        <v>-0.6333</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.2632</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1628</v>
+        <v>-0.3701</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>T. HOLLOWELL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.692</v>
+        <v>-4.7253</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8616</v>
+        <v>-2.6996</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8305</v>
+        <v>-2.0257</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.3323</v>
+        <v>-4.7596</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0579</v>
+        <v>-1.8583</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.2743</v>
+        <v>-2.9013</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.1696</v>
+        <v>-2.1808</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.3806</v>
+        <v>-0.5959</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.789</v>
+        <v>-1.5849</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1627</v>
+        <v>-2.5788</v>
       </c>
       <c r="N25" t="n">
-        <v>1.3227</v>
+        <v>-1.2624</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.4854</v>
+        <v>-1.3164</v>
       </c>
       <c r="P25" t="n">
-        <v>1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R25" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6648</v>
+        <v>-0.8781</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.822</v>
+        <v>-0.5612</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8429</v>
+        <v>-0.317</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W25" t="n">
         <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.5923</v>
+        <v>-9.122</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.1755</v>
+        <v>-6.1757</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.4169</v>
+        <v>-2.9467</v>
       </c>
       <c r="G26" t="n">
         <v>-5.662000000000001</v>
@@ -2452,16 +2452,16 @@
         <v>1.5655</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.2274</v>
+        <v>-7.227399999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9827999999999997</v>
+        <v>-0.9828000000000006</v>
       </c>
       <c r="K26" t="n">
         <v>-2.1267</v>
       </c>
       <c r="L26" t="n">
-        <v>1.1437</v>
+        <v>1.143700000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-4.679</v>
@@ -2470,10 +2470,10 @@
         <v>3.6921</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.3713</v>
+        <v>-8.371300000000002</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.087599999999999</v>
+        <v>-1.0876</v>
       </c>
       <c r="Q26" t="n">
         <v>-13.0502</v>
@@ -2482,13 +2482,13 @@
         <v>11.9626</v>
       </c>
       <c r="S26" t="n">
-        <v>-9.102799999999998</v>
+        <v>-4.6324</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8410999999999998</v>
+        <v>0.8411999999999996</v>
       </c>
       <c r="U26" t="n">
-        <v>-9.944200000000002</v>
+        <v>-5.4738</v>
       </c>
       <c r="V26" t="n">
         <v>2.26</v>
